--- a/backend-server/src/seed/data.xlsx
+++ b/backend-server/src/seed/data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Quiz Bowl 1st Runner Up</t>
   </si>
   <si>
-    <t xml:space="preserve">ICpEP 2026 Convention (Regionals)</t>
+    <t xml:space="preserve">ICpEP 2026 Regional Convention</t>
   </si>
   <si>
     <t xml:space="preserve">Team Member</t>
@@ -64,7 +64,10 @@
     <t xml:space="preserve">ICpEP 2026 Regional MLBB Tournament</t>
   </si>
   <si>
-    <t xml:space="preserve">NCIII Passer</t>
+    <t xml:space="preserve">2025-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCIII Certified</t>
   </si>
   <si>
     <t xml:space="preserve">Java Programming</t>
@@ -73,6 +76,24 @@
     <t xml:space="preserve">Prompt Engineering Trainee</t>
   </si>
   <si>
+    <t xml:space="preserve">Lifewood Data Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TechSTART: CyberSafe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity Workshop and Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">News Writer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Working Hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-present</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jack of All Trades Master of None</t>
   </si>
   <si>
@@ -83,6 +104,117 @@
   </si>
   <si>
     <t xml:space="preserve">DOST Scholar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government Scholar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CpE Challenge Python Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-Stack Web Developer Trainee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Summit Champion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitching Competition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICpEP Regionals 2024 and 2026 Esports Division Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICpEP-R7 CPE Convention </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treasurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICpEP.SE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic Committe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Events Coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creative Member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vice-President External</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danao City Scholar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023 - present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secretary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">President</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House of Representative- CpE Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosplay - CpE Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasundayag 2023-2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membership Committee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil Service Passer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic Committee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 - 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CpEP 2026 Regional Convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd Runner Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICPEP Convention National Python Programming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICPEP Convention Regional Python Programming</t>
   </si>
 </sst>
 </file>
@@ -92,7 +224,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -116,9 +248,25 @@
       <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -165,7 +313,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -178,8 +326,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -372,141 +528,591 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="51.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>3230097</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>3235077</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3235077</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>3230062</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>3230049</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
+        <v>3230049</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>3230049</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
+        <v>3230049</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
+        <v>3230060</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
+        <v>3230055</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
+        <v>3230055</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
+        <v>3230055</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="n">
+        <v>3230055</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
+        <v>3230064</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
+        <v>3230064</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
+        <v>3230044</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
+        <v>3230064</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
+        <v>3230043</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
+        <v>3230051</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="n">
+        <v>3230051</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="n">
+        <v>3230122</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="n">
+        <v>3230122</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="n">
+        <v>3230122</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="n">
+        <v>3230228</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="n">
+        <v>3230228</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="n">
+        <v>3230099</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="n">
+        <v>3230099</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="n">
+        <v>3230099</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="n">
+        <v>3230026</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="n">
+        <v>3230026</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="n">
+        <v>3230026</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="n">
+        <v>3230026</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="C33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="4" t="n">
         <v>2024</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>3230049</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="3" t="n">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="n">
+        <v>3230047</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="n">
+        <v>3230047</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="n">
+        <v>3231315</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="n">
+        <v>3231315</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="n">
+        <v>3230098</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="n">
+        <v>3230039</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="n">
+        <v>3230039</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>3230060</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
-        <v>3230055</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="n">
+        <v>3230039</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C19" r:id="rId1" display="ICpEP.SE "/>
+    <hyperlink ref="C20" r:id="rId2" display="ICpEP.SE "/>
+    <hyperlink ref="C22" r:id="rId3" display="ICpEP.SE "/>
+    <hyperlink ref="C23" r:id="rId4" display="ICpEP.SE "/>
+    <hyperlink ref="C25" r:id="rId5" display="ICpEP.SE "/>
+    <hyperlink ref="C26" r:id="rId6" display="ICpEP.SE "/>
+    <hyperlink ref="C27" r:id="rId7" display="ICpEP.SE "/>
+    <hyperlink ref="C28" r:id="rId8" display="ICpEP.SE "/>
+    <hyperlink ref="C30" r:id="rId9" display="ICpEP.SE "/>
+    <hyperlink ref="C34" r:id="rId10" display="ICpEP.SE "/>
+    <hyperlink ref="C36" r:id="rId11" display="ICpEP.SE "/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
